--- a/data/trans_dic/P3A_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,02</t>
+          <t>2,68; 7,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,99</t>
+          <t>1,19; 5,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,98</t>
+          <t>1,17; 4,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,39</t>
+          <t>2,63; 7,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,25</t>
+          <t>0,87; 5,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,51</t>
+          <t>2,17; 7,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,19</t>
+          <t>1,38; 6,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 7,85</t>
+          <t>3,87; 7,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,4</t>
+          <t>2,3; 5,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,24</t>
+          <t>2,08; 5,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,68</t>
+          <t>1,41; 4,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 6,67</t>
+          <t>3,8; 6,73</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,97</t>
+          <t>2,18; 6,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,03</t>
+          <t>1,2; 4,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,58</t>
+          <t>0,62; 2,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,63</t>
+          <t>1,87; 5,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,59</t>
+          <t>2,0; 5,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,85</t>
+          <t>2,76; 6,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,18</t>
+          <t>1,09; 4,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,32</t>
+          <t>3,49; 6,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,08</t>
+          <t>2,52; 5,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,9</t>
+          <t>2,46; 4,91</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,06</t>
+          <t>1,06; 2,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,22</t>
+          <t>2,95; 5,34</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,78</t>
+          <t>2,39; 6,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 9,19</t>
+          <t>3,7; 9,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,64</t>
+          <t>1,27; 4,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 9,53</t>
+          <t>4,53; 9,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,79</t>
+          <t>2,22; 6,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 8,11</t>
+          <t>2,98; 7,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,81</t>
+          <t>0,64; 3,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 12,18</t>
+          <t>6,86; 11,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,98</t>
+          <t>2,85; 5,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,76</t>
+          <t>3,8; 7,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,43</t>
+          <t>1,22; 3,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,41; 9,7</t>
+          <t>6,36; 9,76</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,05</t>
+          <t>1,85; 5,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,3</t>
+          <t>1,63; 5,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,71</t>
+          <t>0,45; 2,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 13,02</t>
+          <t>5,43; 12,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,01</t>
+          <t>3,33; 8,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,67</t>
+          <t>2,08; 5,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 6,26</t>
+          <t>1,41; 5,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,43</t>
+          <t>3,12; 7,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,04</t>
+          <t>3,19; 6,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,76</t>
+          <t>2,21; 4,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,77</t>
+          <t>1,17; 3,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,67; 8,61</t>
+          <t>4,49; 8,69</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,72</t>
+          <t>1,33; 6,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 9,43</t>
+          <t>2,5; 9,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,72</t>
+          <t>1,58; 5,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 4,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,42</t>
+          <t>2,36; 8,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,09</t>
+          <t>0,42; 4,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,0</t>
+          <t>1,72; 5,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,89</t>
+          <t>0,95; 4,08</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 7,36</t>
+          <t>2,95; 7,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,7</t>
+          <t>0,43; 2,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,65</t>
+          <t>2,19; 4,92</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,9</t>
+          <t>2,43; 7,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,95; 13,62</t>
+          <t>6,69; 13,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,37</t>
+          <t>1,2; 5,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,19</t>
+          <t>4,39; 8,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,7</t>
+          <t>0,42; 3,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,59</t>
+          <t>2,26; 7,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,07</t>
+          <t>3,13; 9,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 12,24</t>
+          <t>6,93; 12,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,65</t>
+          <t>1,84; 4,84</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,23</t>
+          <t>4,8; 9,27</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,96</t>
+          <t>2,54; 6,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,26; 9,64</t>
+          <t>6,21; 9,32</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,95</t>
+          <t>2,03; 4,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,88</t>
+          <t>1,76; 4,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,59</t>
+          <t>2,37; 5,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,84; 8,28</t>
+          <t>4,01; 8,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,51</t>
+          <t>1,64; 4,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,46; 7,38</t>
+          <t>3,59; 7,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,78</t>
+          <t>2,57; 5,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,11</t>
+          <t>2,3; 7,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,09</t>
+          <t>2,22; 4,16</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,46</t>
+          <t>3,08; 5,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,0</t>
+          <t>2,77; 5,04</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,7</t>
+          <t>3,35; 6,91</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,69</t>
+          <t>3,52; 6,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,55</t>
+          <t>2,08; 4,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,34</t>
+          <t>1,92; 4,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,33</t>
+          <t>0,55; 2,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,8</t>
+          <t>2,11; 4,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,94</t>
+          <t>3,2; 6,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,34</t>
+          <t>1,9; 4,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,6</t>
+          <t>2,57; 4,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,12; 5,23</t>
+          <t>3,07; 5,13</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,9</t>
+          <t>2,93; 4,92</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,94</t>
+          <t>2,12; 3,87</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,07</t>
+          <t>1,46; 3,16</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,36; 4,77</t>
+          <t>3,4; 4,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,51</t>
+          <t>3,13; 4,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,01</t>
+          <t>1,9; 2,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,19</t>
+          <t>3,34; 5,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,59; 3,81</t>
+          <t>2,55; 3,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,42</t>
+          <t>3,81; 5,3</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,73</t>
+          <t>2,48; 3,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,46; 6,02</t>
+          <t>4,23; 6,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,08</t>
+          <t>3,15; 4,06</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,72; 4,69</t>
+          <t>3,75; 4,71</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,18</t>
+          <t>2,3; 3,16</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,45</t>
+          <t>4,18; 5,44</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7372; 21892</t>
+          <t>7324; 20880</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3545; 14717</t>
+          <t>3499; 14787</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3236; 14642</t>
+          <t>3446; 14467</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8934; 23016</t>
+          <t>8186; 22410</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2320; 13634</t>
+          <t>2268; 13794</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6474; 21573</t>
+          <t>6231; 20304</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3643; 17884</t>
+          <t>3973; 18848</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10684; 22724</t>
+          <t>11205; 23142</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11015; 28768</t>
+          <t>12262; 31001</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11866; 30496</t>
+          <t>12087; 30436</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9619; 27266</t>
+          <t>8239; 26478</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22681; 40116</t>
+          <t>22819; 40442</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10516; 29432</t>
+          <t>10726; 30066</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5159; 20313</t>
+          <t>6043; 22071</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2763; 12851</t>
+          <t>3071; 13352</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9861; 29204</t>
+          <t>9677; 29152</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10076; 28177</t>
+          <t>10099; 27128</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15403; 35866</t>
+          <t>14458; 36454</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5165; 21832</t>
+          <t>5692; 21252</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17619; 32553</t>
+          <t>17965; 32823</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24885; 50638</t>
+          <t>25101; 51359</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24068; 50415</t>
+          <t>25297; 50502</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11185; 31214</t>
+          <t>10820; 29900</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31494; 53944</t>
+          <t>30512; 55134</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7726; 21607</t>
+          <t>7633; 21267</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12107; 29779</t>
+          <t>11977; 29390</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3915; 14741</t>
+          <t>4039; 15531</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14277; 30068</t>
+          <t>14285; 29590</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7424; 22782</t>
+          <t>7450; 22457</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10477; 27668</t>
+          <t>10153; 27020</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2144; 12797</t>
+          <t>2137; 12695</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24601; 42375</t>
+          <t>23864; 40973</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18701; 39154</t>
+          <t>18637; 38601</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26066; 51630</t>
+          <t>25279; 51168</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8111; 22434</t>
+          <t>7993; 22853</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42514; 64353</t>
+          <t>42194; 64750</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6681; 21701</t>
+          <t>6619; 21468</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5281; 19819</t>
+          <t>6081; 20407</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1641; 9993</t>
+          <t>1640; 10497</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16726; 40698</t>
+          <t>16966; 39895</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12536; 29675</t>
+          <t>12334; 30437</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7145; 22062</t>
+          <t>8099; 23033</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5386; 24229</t>
+          <t>5445; 23123</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15185; 35337</t>
+          <t>14849; 35350</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22472; 44023</t>
+          <t>23235; 44268</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14995; 36334</t>
+          <t>16841; 37239</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8703; 28501</t>
+          <t>8823; 27225</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36784; 67857</t>
+          <t>35356; 68473</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2651; 13657</t>
+          <t>2712; 13520</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5394; 20051</t>
+          <t>5311; 19838</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6990</t>
+          <t>0; 6985</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2925; 10194</t>
+          <t>2819; 9803</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6796</t>
+          <t>0; 8417</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5095; 18497</t>
+          <t>5174; 18533</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>911; 8912</t>
+          <t>916; 9362</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4159; 12942</t>
+          <t>4449; 13702</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4175; 15985</t>
+          <t>3916; 16751</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13359; 31817</t>
+          <t>12739; 31609</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1930; 11595</t>
+          <t>1850; 10371</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8937; 20330</t>
+          <t>9568; 21504</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6647; 21394</t>
+          <t>6585; 20782</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16301; 37329</t>
+          <t>18333; 37154</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3484; 14055</t>
+          <t>3150; 13294</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11674; 22091</t>
+          <t>11824; 23273</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1036; 10298</t>
+          <t>1170; 10933</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6332; 21255</t>
+          <t>6318; 20334</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7403; 24687</t>
+          <t>8514; 25109</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17826; 31462</t>
+          <t>17809; 31648</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9891; 25522</t>
+          <t>10120; 26581</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27102; 51127</t>
+          <t>26570; 51335</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13580; 31796</t>
+          <t>13535; 32254</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>32997; 50766</t>
+          <t>32683; 49068</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12400; 30422</t>
+          <t>12510; 30697</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12335; 32361</t>
+          <t>11687; 32547</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14875; 36649</t>
+          <t>15528; 36745</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23963; 51667</t>
+          <t>25028; 51532</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10501; 28650</t>
+          <t>10415; 29009</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23990; 51202</t>
+          <t>24921; 50107</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17439; 39846</t>
+          <t>17746; 38867</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>19906; 60365</t>
+          <t>19516; 61554</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26583; 51204</t>
+          <t>27769; 52076</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40693; 74079</t>
+          <t>41786; 75746</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37159; 67200</t>
+          <t>37208; 67733</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>46045; 98701</t>
+          <t>49392; 101848</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>26600; 49718</t>
+          <t>26157; 50186</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15501; 35482</t>
+          <t>16181; 35012</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14301; 33815</t>
+          <t>14957; 33693</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5037; 21611</t>
+          <t>5081; 22847</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>16881; 37595</t>
+          <t>16568; 37269</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24303; 48780</t>
+          <t>26285; 50226</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14820; 35873</t>
+          <t>15677; 37670</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>18187; 33023</t>
+          <t>18426; 33680</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>47687; 79840</t>
+          <t>46804; 78253</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>46824; 78476</t>
+          <t>46857; 78812</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>34193; 63179</t>
+          <t>33947; 62177</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>22504; 50530</t>
+          <t>24035; 52075</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>110225; 156128</t>
+          <t>111528; 161196</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>107733; 154617</t>
+          <t>107120; 156295</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>66300; 101792</t>
+          <t>64369; 100996</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>115754; 179417</t>
+          <t>115599; 174998</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>87566; 128710</t>
+          <t>86206; 126266</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>139713; 192863</t>
+          <t>135629; 188487</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>84935; 132123</t>
+          <t>87941; 132776</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>165465; 223279</t>
+          <t>157053; 225152</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>211408; 271328</t>
+          <t>209386; 269777</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>260008; 327290</t>
+          <t>261714; 328811</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>162745; 220265</t>
+          <t>158996; 218791</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>303718; 390597</t>
+          <t>299741; 389766</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R2-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,65</t>
+          <t>2,81; 7,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,02</t>
+          <t>1,26; 4,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,92</t>
+          <t>0,92; 5,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,2</t>
+          <t>2,82; 6,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,31</t>
+          <t>0,89; 5,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,07</t>
+          <t>2,23; 7,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,53</t>
+          <t>1,39; 6,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,99</t>
+          <t>3,76; 7,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 5,82</t>
+          <t>2,27; 5,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,23</t>
+          <t>2,06; 5,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,55</t>
+          <t>1,57; 4,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,73</t>
+          <t>3,62; 6,25</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,1</t>
+          <t>2,2; 5,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,38</t>
+          <t>1,18; 4,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,68</t>
+          <t>0,57; 2,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,62</t>
+          <t>1,95; 5,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,38</t>
+          <t>1,99; 5,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,96</t>
+          <t>2,93; 6,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,07</t>
+          <t>1,07; 4,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 6,37</t>
+          <t>3,48; 6,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,15</t>
+          <t>2,42; 5,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,91</t>
+          <t>2,39; 4,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,93</t>
+          <t>1,04; 2,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,34</t>
+          <t>3,09; 5,45</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,67</t>
+          <t>2,39; 6,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 9,07</t>
+          <t>3,72; 9,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,89</t>
+          <t>1,24; 4,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 9,38</t>
+          <t>4,46; 9,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,7</t>
+          <t>2,25; 6,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 7,92</t>
+          <t>2,92; 8,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,77</t>
+          <t>0,63; 3,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,78</t>
+          <t>7,06; 11,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 5,9</t>
+          <t>2,78; 5,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,69</t>
+          <t>4,01; 7,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,49</t>
+          <t>1,19; 3,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,76</t>
+          <t>6,4; 9,82</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,99</t>
+          <t>2,08; 5,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,46</t>
+          <t>1,75; 5,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,85</t>
+          <t>0,44; 2,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 12,76</t>
+          <t>5,13; 12,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,22</t>
+          <t>3,41; 7,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,92</t>
+          <t>1,82; 5,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,97</t>
+          <t>1,32; 6,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,43</t>
+          <t>4,79; 8,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,07</t>
+          <t>3,05; 6,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,88</t>
+          <t>2,21; 4,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,6</t>
+          <t>1,13; 3,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 8,69</t>
+          <t>5,61; 9,62</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,65</t>
+          <t>1,3; 6,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 9,33</t>
+          <t>2,42; 9,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 2,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,5</t>
+          <t>1,41; 5,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 8,44</t>
+          <t>2,32; 8,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,3</t>
+          <t>0,42; 3,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,29</t>
+          <t>2,57; 5,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,08</t>
+          <t>1,04; 3,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,31</t>
+          <t>3,04; 7,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,42</t>
+          <t>0,44; 2,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,92</t>
+          <t>2,39; 4,83</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,67</t>
+          <t>2,48; 7,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,69; 13,56</t>
+          <t>6,07; 13,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,08</t>
+          <t>1,25; 5,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,63</t>
+          <t>4,39; 8,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,93</t>
+          <t>0,37; 3,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,26</t>
+          <t>2,19; 7,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,13; 9,23</t>
+          <t>2,86; 9,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 12,31</t>
+          <t>6,73; 12,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,84</t>
+          <t>1,89; 4,91</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,8; 9,27</t>
+          <t>4,89; 9,14</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,04</t>
+          <t>2,63; 6,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,21; 9,32</t>
+          <t>6,13; 9,3</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,99</t>
+          <t>1,88; 4,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,91</t>
+          <t>1,9; 4,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,61</t>
+          <t>2,39; 5,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,01; 8,25</t>
+          <t>4,26; 8,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,56</t>
+          <t>1,73; 4,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,22</t>
+          <t>3,4; 7,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,64</t>
+          <t>2,52; 5,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,25</t>
+          <t>5,53; 8,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,16</t>
+          <t>2,14; 4,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,58</t>
+          <t>3,01; 5,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,04</t>
+          <t>2,8; 4,94</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,35; 6,91</t>
+          <t>5,22; 7,68</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,76</t>
+          <t>3,48; 6,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,49</t>
+          <t>2,14; 4,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,33</t>
+          <t>1,85; 4,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,46</t>
+          <t>1,09; 2,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,76</t>
+          <t>2,12; 4,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,11</t>
+          <t>2,94; 5,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,56</t>
+          <t>1,83; 4,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,69</t>
+          <t>2,64; 4,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,13</t>
+          <t>3,03; 5,1</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,92</t>
+          <t>2,94; 4,84</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,87</t>
+          <t>2,13; 4,0</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,16</t>
+          <t>2,11; 3,55</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,4; 4,92</t>
+          <t>3,41; 4,8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,13; 4,56</t>
+          <t>3,11; 4,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,98</t>
+          <t>1,96; 2,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,06</t>
+          <t>3,94; 5,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,74</t>
+          <t>2,57; 3,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,3</t>
+          <t>3,81; 5,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,48; 3,75</t>
+          <t>2,48; 3,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,23; 6,07</t>
+          <t>5,22; 6,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,06</t>
+          <t>3,18; 4,06</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,75; 4,71</t>
+          <t>3,68; 4,72</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,3; 3,16</t>
+          <t>2,35; 3,2</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,18; 5,44</t>
+          <t>4,77; 5,73</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14596</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16259</t>
+          <t>16775</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30854</t>
+          <t>30566</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7324; 20880</t>
+          <t>7673; 21212</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3499; 14787</t>
+          <t>3726; 14454</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3446; 14467</t>
+          <t>2699; 15045</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8186; 22410</t>
+          <t>8994; 21951</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2268; 13794</t>
+          <t>2323; 13033</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6231; 20304</t>
+          <t>6402; 21695</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3973; 18848</t>
+          <t>4015; 18329</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11205; 23142</t>
+          <t>11883; 23620</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12262; 31001</t>
+          <t>12081; 29741</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12087; 30436</t>
+          <t>11972; 30329</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8239; 26478</t>
+          <t>9168; 27370</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22819; 40442</t>
+          <t>22961; 39704</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17068</t>
+          <t>17951</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24130</t>
+          <t>25983</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41198</t>
+          <t>43934</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10726; 30066</t>
+          <t>10834; 29534</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6043; 22071</t>
+          <t>5973; 22616</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3071; 13352</t>
+          <t>2845; 12734</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9677; 29152</t>
+          <t>10349; 30033</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10099; 27128</t>
+          <t>10054; 26640</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14458; 36454</t>
+          <t>15356; 36259</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5692; 21252</t>
+          <t>5593; 20953</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17965; 32823</t>
+          <t>19023; 34587</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25101; 51359</t>
+          <t>24162; 50321</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25297; 50502</t>
+          <t>24542; 48866</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10820; 29900</t>
+          <t>10655; 30204</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30512; 55134</t>
+          <t>33329; 58692</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21023</t>
+          <t>20426</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31991</t>
+          <t>32160</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53014</t>
+          <t>52586</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7633; 21267</t>
+          <t>7622; 21703</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11977; 29390</t>
+          <t>12064; 29623</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4039; 15531</t>
+          <t>3934; 14831</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14285; 29590</t>
+          <t>14079; 28514</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7450; 22457</t>
+          <t>7561; 22534</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10153; 27020</t>
+          <t>9960; 27859</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2137; 12695</t>
+          <t>2124; 12450</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23864; 40973</t>
+          <t>25078; 42517</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18637; 38601</t>
+          <t>18193; 37569</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25279; 51168</t>
+          <t>26656; 50173</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7993; 22853</t>
+          <t>7800; 23230</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42194; 64750</t>
+          <t>42884; 65821</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25421</t>
+          <t>30026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25548</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50969</t>
+          <t>57250</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6619; 21468</t>
+          <t>7444; 21182</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6081; 20407</t>
+          <t>6558; 20229</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1640; 10497</t>
+          <t>1634; 9730</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16966; 39895</t>
+          <t>19147; 46093</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12334; 30437</t>
+          <t>12632; 29064</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8099; 23033</t>
+          <t>7084; 22500</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5445; 23123</t>
+          <t>5102; 24249</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14849; 35350</t>
+          <t>20208; 35808</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23235; 44268</t>
+          <t>22209; 43763</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16841; 37239</t>
+          <t>16885; 36801</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8823; 27225</t>
+          <t>8551; 28651</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35356; 68473</t>
+          <t>44603; 76454</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14338</t>
+          <t>15040</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2712; 13520</t>
+          <t>2652; 13726</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5311; 19838</t>
+          <t>5136; 20179</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6985</t>
+          <t>0; 5879</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2819; 9803</t>
+          <t>2883; 10779</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 8417</t>
+          <t>0; 6494</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5174; 18533</t>
+          <t>5095; 17856</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>916; 9362</t>
+          <t>909; 8637</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4449; 13702</t>
+          <t>5874; 13418</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3916; 16751</t>
+          <t>4275; 16204</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12739; 31609</t>
+          <t>13142; 31650</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1850; 10371</t>
+          <t>1899; 11294</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>9568; 21504</t>
+          <t>10373; 20987</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>16504</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>23809</t>
+          <t>23959</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6585; 20782</t>
+          <t>6709; 20425</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18333; 37154</t>
+          <t>16643; 36992</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3150; 13294</t>
+          <t>3277; 13430</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11824; 23273</t>
+          <t>11883; 22586</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1170; 10933</t>
+          <t>1036; 9389</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6318; 20334</t>
+          <t>6137; 20543</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8514; 25109</t>
+          <t>7788; 24991</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17809; 31648</t>
+          <t>17755; 31831</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>10120; 26581</t>
+          <t>10362; 26957</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26570; 51335</t>
+          <t>27113; 50620</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13535; 32254</t>
+          <t>14047; 33355</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>32683; 49068</t>
+          <t>32749; 49715</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35300</t>
+          <t>41930</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>43165</t>
+          <t>53127</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>78465</t>
+          <t>95057</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12510; 30697</t>
+          <t>11571; 30126</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11687; 32547</t>
+          <t>12603; 32225</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15528; 36745</t>
+          <t>15698; 37048</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25028; 51532</t>
+          <t>30684; 58011</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10415; 29009</t>
+          <t>11017; 28595</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24921; 50107</t>
+          <t>23626; 49556</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17746; 38867</t>
+          <t>17369; 39485</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>19516; 61554</t>
+          <t>42661; 65094</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>27769; 52076</t>
+          <t>26755; 50679</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>41786; 75746</t>
+          <t>40861; 74256</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37208; 67733</t>
+          <t>37618; 66406</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>49392; 101848</t>
+          <t>77938; 114510</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>14870</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>25113</t>
+          <t>30011</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>38479</t>
+          <t>44881</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>26157; 50186</t>
+          <t>25880; 50825</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>16181; 35012</t>
+          <t>16654; 36152</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14957; 33693</t>
+          <t>14419; 34007</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5081; 22847</t>
+          <t>8728; 22917</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>16568; 37269</t>
+          <t>16586; 35794</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26285; 50226</t>
+          <t>24137; 49036</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15677; 37670</t>
+          <t>15155; 37881</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>18426; 33680</t>
+          <t>21989; 39399</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>46804; 78253</t>
+          <t>46224; 77823</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>46857; 78812</t>
+          <t>47061; 77419</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33947; 62177</t>
+          <t>34156; 64206</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>24035; 52075</t>
+          <t>34307; 57874</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>149050</t>
+          <t>161420</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>198729</t>
+          <t>218358</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>347779</t>
+          <t>379778</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>111528; 161196</t>
+          <t>111755; 157176</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>107120; 156295</t>
+          <t>106620; 154326</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>64369; 100996</t>
+          <t>66300; 100802</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>115599; 174998</t>
+          <t>139060; 189508</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>86206; 126266</t>
+          <t>86834; 128260</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>135629; 188487</t>
+          <t>135337; 187871</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>87941; 132776</t>
+          <t>87896; 132928</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>157053; 225152</t>
+          <t>195052; 241052</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>209386; 269777</t>
+          <t>211271; 270028</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>261714; 328811</t>
+          <t>256649; 329203</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>158996; 218791</t>
+          <t>162606; 221779</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>299741; 389766</t>
+          <t>346329; 416088</t>
         </is>
       </c>
     </row>
